--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -202,6 +202,18 @@
   </si>
   <si>
     <t>I felt tired after last two class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfied </t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>I felt good after all class.</t>
   </si>
 </sst>
 </file>
@@ -1024,26 +1036,49 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
-        <f t="shared" ref="I7:I69" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
-        <f t="shared" ref="J6:J69" si="1">IF(I7="","",1440-I7)</f>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+      <c r="A7" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B7" s="14">
+        <v>450</v>
+      </c>
+      <c r="C7" s="14">
+        <v>50</v>
+      </c>
+      <c r="D7" s="14">
+        <v>120</v>
+      </c>
+      <c r="E7" s="14">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14">
+        <v>150</v>
+      </c>
+      <c r="G7" s="14">
+        <v>3</v>
+      </c>
+      <c r="H7" s="14">
+        <v>120</v>
+      </c>
+      <c r="I7" s="15">
+        <v>950</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" ref="J7:J69" si="0">IF(I7="","",1440-I7)</f>
+        <v>490</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="13"/>
@@ -1055,11 +1090,11 @@
       <c r="G8" s="14"/>
       <c r="H8" s="14"/>
       <c r="I8" s="15" t="str">
+        <f t="shared" ref="I7:I69" si="1">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
+        <v/>
+      </c>
+      <c r="J8" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K8" s="16"/>
@@ -1077,11 +1112,11 @@
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
       <c r="I9" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J9" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K9" s="16"/>
@@ -1099,11 +1134,11 @@
       <c r="G10" s="14"/>
       <c r="H10" s="14"/>
       <c r="I10" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J10" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K10" s="16"/>
@@ -1121,11 +1156,11 @@
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
       <c r="I11" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J11" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K11" s="16"/>
@@ -1143,11 +1178,11 @@
       <c r="G12" s="14"/>
       <c r="H12" s="14"/>
       <c r="I12" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J12" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K12" s="16"/>
@@ -1165,11 +1200,11 @@
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
       <c r="I13" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J13" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K13" s="16"/>
@@ -1187,11 +1222,11 @@
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J14" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K14" s="16"/>
@@ -1209,11 +1244,11 @@
       <c r="G15" s="14"/>
       <c r="H15" s="14"/>
       <c r="I15" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J15" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K15" s="16"/>
@@ -1231,11 +1266,11 @@
       <c r="G16" s="14"/>
       <c r="H16" s="14"/>
       <c r="I16" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J16" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K16" s="16"/>
@@ -1253,11 +1288,11 @@
       <c r="G17" s="14"/>
       <c r="H17" s="14"/>
       <c r="I17" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J17" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K17" s="16"/>
@@ -1275,11 +1310,11 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
       <c r="I18" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J18" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K18" s="16"/>
@@ -1297,11 +1332,11 @@
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
       <c r="I19" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J19" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K19" s="16"/>
@@ -1319,11 +1354,11 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
       <c r="I20" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J20" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K20" s="16"/>
@@ -1341,11 +1376,11 @@
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
       <c r="I21" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J21" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K21" s="16"/>
@@ -1363,11 +1398,11 @@
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
       <c r="I22" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J22" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K22" s="16"/>
@@ -1385,11 +1420,11 @@
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
       <c r="I23" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J23" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K23" s="16"/>
@@ -1407,11 +1442,11 @@
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
       <c r="I24" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J24" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K24" s="16"/>
@@ -1429,11 +1464,11 @@
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="I25" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J25" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K25" s="16"/>
@@ -1451,11 +1486,11 @@
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
       <c r="I26" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J26" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K26" s="16"/>
@@ -1473,11 +1508,11 @@
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="I27" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J27" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K27" s="16"/>
@@ -1495,11 +1530,11 @@
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
       <c r="I28" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J28" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K28" s="16"/>
@@ -1517,11 +1552,11 @@
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
       <c r="I29" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J29" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K29" s="16"/>
@@ -1539,11 +1574,11 @@
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="I30" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J30" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K30" s="16"/>
@@ -1561,11 +1596,11 @@
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
       <c r="I31" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J31" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K31" s="16"/>
@@ -1583,11 +1618,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="I32" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J32" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K32" s="16"/>
@@ -1605,11 +1640,11 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
       <c r="I33" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J33" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K33" s="16"/>
@@ -1627,11 +1662,11 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
       <c r="I34" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J34" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K34" s="16"/>
@@ -1649,11 +1684,11 @@
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
       <c r="I35" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J35" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K35" s="16"/>
@@ -1671,11 +1706,11 @@
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
       <c r="I36" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J36" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K36" s="16"/>
@@ -1693,11 +1728,11 @@
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
       <c r="I37" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J37" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K37" s="16"/>
@@ -1715,11 +1750,11 @@
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
       <c r="I38" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J38" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K38" s="16"/>
@@ -1737,11 +1772,11 @@
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
       <c r="I39" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J39" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K39" s="16"/>
@@ -1759,11 +1794,11 @@
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
       <c r="I40" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J40" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K40" s="16"/>
@@ -1781,11 +1816,11 @@
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J41" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K41" s="16"/>
@@ -1803,11 +1838,11 @@
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J42" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K42" s="16"/>
@@ -1825,11 +1860,11 @@
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J43" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K43" s="16"/>
@@ -1847,11 +1882,11 @@
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
       <c r="I44" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J44" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K44" s="16"/>
@@ -1869,11 +1904,11 @@
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
       <c r="I45" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J45" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K45" s="16"/>
@@ -1891,11 +1926,11 @@
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
       <c r="I46" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J46" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K46" s="16"/>
@@ -1913,11 +1948,11 @@
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
       <c r="I47" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J47" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K47" s="16"/>
@@ -1935,11 +1970,11 @@
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
       <c r="I48" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J48" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K48" s="16"/>
@@ -1957,11 +1992,11 @@
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J49" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K49" s="16"/>
@@ -1979,11 +2014,11 @@
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
       <c r="I50" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J50" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K50" s="16"/>
@@ -2001,11 +2036,11 @@
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
       <c r="I51" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J51" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K51" s="16"/>
@@ -2023,11 +2058,11 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
       <c r="I52" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J52" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K52" s="16"/>
@@ -2045,11 +2080,11 @@
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J53" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K53" s="16"/>
@@ -2067,11 +2102,11 @@
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
       <c r="I54" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J54" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K54" s="16"/>
@@ -2089,11 +2124,11 @@
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
       <c r="I55" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J55" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K55" s="16"/>
@@ -2111,11 +2146,11 @@
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
       <c r="I56" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J56" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K56" s="16"/>
@@ -2133,11 +2168,11 @@
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J57" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K57" s="16"/>
@@ -2155,11 +2190,11 @@
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
       <c r="I58" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J58" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K58" s="16"/>
@@ -2177,11 +2212,11 @@
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
       <c r="I59" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J59" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K59" s="16"/>
@@ -2199,11 +2234,11 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J60" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K60" s="16"/>
@@ -2221,11 +2256,11 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J61" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K61" s="16"/>
@@ -2243,11 +2278,11 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J62" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K62" s="16"/>
@@ -2265,11 +2300,11 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J63" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K63" s="16"/>
@@ -2287,11 +2322,11 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J64" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K64" s="16"/>
@@ -2309,11 +2344,11 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J65" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K65" s="16"/>
@@ -2331,11 +2366,11 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J66" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K66" s="16"/>
@@ -2353,11 +2388,11 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J67" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K67" s="16"/>
@@ -2375,11 +2410,11 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J68" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -2397,11 +2432,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J69" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K69" s="16"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,15 @@
   </si>
   <si>
     <t>I felt good after all class.</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>I felt tired after last class.</t>
   </si>
 </sst>
 </file>
@@ -1081,26 +1090,50 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
-        <f t="shared" ref="I7:I69" si="1">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>50</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>250</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>120</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" ref="I8:I69" si="1">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
+        <v>1080</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -189,9 +189,6 @@
     <t>August</t>
   </si>
   <si>
-    <t>MCA / D1P2631</t>
-  </si>
-  <si>
     <t>satisfied</t>
   </si>
   <si>
@@ -223,6 +220,15 @@
   </si>
   <si>
     <t>I felt tired after last class.</t>
+  </si>
+  <si>
+    <t>I felt tired from play cricket.</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>MCA/D1P2631</t>
   </si>
 </sst>
 </file>
@@ -926,7 +932,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1032,16 +1038,16 @@
         <v>550</v>
       </c>
       <c r="K6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" s="12" t="s">
         <v>55</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1077,16 +1083,16 @@
         <v>490</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="M7" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="N7" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1123,39 +1129,63 @@
         <v>360</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="N8" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="N8" s="17" t="s">
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B9" s="14">
+        <v>450</v>
+      </c>
+      <c r="C9" s="14">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14">
+        <v>180</v>
+      </c>
+      <c r="E9" s="14">
+        <v>120</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>180</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>MCA/D1P2631</t>
+  </si>
+  <si>
+    <t>I felt good.</t>
   </si>
 </sst>
 </file>
@@ -1188,26 +1191,50 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>180</v>
+      </c>
+      <c r="E10" s="14">
+        <v>90</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>210</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1237,26 +1237,50 @@
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>50</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>350</v>
+      </c>
+      <c r="G11" s="14">
+        <v>7</v>
+      </c>
+      <c r="H11" s="14">
+        <v>40</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>I felt good.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">satisfied </t>
+  </si>
+  <si>
+    <t>I felt good after last tow class.</t>
   </si>
 </sst>
 </file>
@@ -1283,26 +1289,50 @@
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
+      <c r="C12" s="14">
+        <v>50</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>90</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,15 @@
   </si>
   <si>
     <t>I felt good after last tow class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> stressed </t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>I felt tired after fresser party.</t>
   </si>
 </sst>
 </file>
@@ -1335,26 +1344,50 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>45</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>400</v>
+      </c>
+      <c r="G13" s="14">
+        <v>8</v>
+      </c>
+      <c r="H13" s="14">
+        <v>30</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>365</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>I felt tired after fresser party.</t>
+  </si>
+  <si>
+    <t>I felt good after last two class.</t>
   </si>
 </sst>
 </file>
@@ -1390,26 +1393,50 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B14" s="14">
+        <v>480</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>90</v>
+      </c>
+      <c r="F14" s="14">
+        <v>150</v>
+      </c>
+      <c r="G14" s="14">
+        <v>3</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>I felt good after last two class.</t>
+  </si>
+  <si>
+    <t>I felt good after class.</t>
   </si>
 </sst>
 </file>
@@ -1439,26 +1442,50 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>50</v>
+      </c>
+      <c r="D15" s="14">
+        <v>180</v>
+      </c>
+      <c r="E15" s="14">
+        <v>90</v>
+      </c>
+      <c r="F15" s="14">
+        <v>50</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>240</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>I felt good after class.</t>
+  </si>
+  <si>
+    <t>I felt tired after night study</t>
   </si>
 </sst>
 </file>
@@ -1488,48 +1491,96 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B16" s="14">
+        <v>480</v>
+      </c>
+      <c r="C16" s="14">
+        <v>60</v>
+      </c>
+      <c r="D16" s="14">
+        <v>200</v>
+      </c>
+      <c r="E16" s="14">
+        <v>150</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>200</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>300</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1583,26 +1583,50 @@
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>45</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>350</v>
+      </c>
+      <c r="G18" s="14">
+        <v>7</v>
+      </c>
+      <c r="H18" s="14">
+        <v>40</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>405</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,12 @@
   </si>
   <si>
     <t>I felt tired after night study</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>I felt tired after two class.</t>
   </si>
 </sst>
 </file>
@@ -1629,48 +1635,96 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B19" s="14">
+        <v>360</v>
+      </c>
+      <c r="C19" s="14">
+        <v>45</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>350</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>40</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>975</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>465</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>45</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>50</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1045</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>395</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>I felt tired after two class.</t>
+  </si>
+  <si>
+    <t>I felt good after last class.</t>
   </si>
 </sst>
 </file>
@@ -1727,26 +1730,50 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>45</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>90</v>
+      </c>
+      <c r="F21" s="14">
+        <v>150</v>
+      </c>
+      <c r="G21" s="14">
+        <v>3</v>
+      </c>
+      <c r="H21" s="14">
+        <v>30</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>525</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>I felt good after last class.</t>
+  </si>
+  <si>
+    <t>I felt tired after go to unimall.</t>
   </si>
 </sst>
 </file>
@@ -1776,26 +1779,50 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B22" s="14">
+        <v>360</v>
+      </c>
+      <c r="C22" s="14">
+        <v>45</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>90</v>
+      </c>
+      <c r="F22" s="14">
+        <v>100</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="14">
+        <v>180</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>895</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>545</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>I felt tired after go to unimall.</t>
+  </si>
+  <si>
+    <t>I flelt good.</t>
   </si>
 </sst>
 </file>
@@ -1825,48 +1828,96 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>45</v>
+      </c>
+      <c r="D23" s="14">
+        <v>180</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
+        <v>50</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14">
+        <v>200</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>955</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>485</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>300</v>
+      </c>
+      <c r="E24" s="14">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13"/>

--- a/12618140.xlsx
+++ b/12618140.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1920,70 +1920,141 @@
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>45</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>350</v>
+      </c>
+      <c r="G25" s="14">
+        <v>7</v>
+      </c>
+      <c r="H25" s="14">
+        <v>40</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>405</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>45</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>40</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>975</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>465</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>45</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14">
+        <v>350</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>995</v>
+      </c>
+      <c r="J27" s="15">
+        <v>445</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13"/>
